--- a/Bigpy/Py_Scrap/data/you_crawl_result.xlsx
+++ b/Bigpy/Py_Scrap/data/you_crawl_result.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="176">
   <si>
     <t>작성자</t>
   </si>
@@ -28,436 +28,573 @@
     <t>프로필이미지</t>
   </si>
   <si>
-    <t>@jihunyang1556</t>
-  </si>
-  <si>
-    <t>삶에대한 열정이나 희망따위는 없어 흘러가는대로 그냥 숨쉬고있을뿐
-무미건조하게 매일 반복되는 일상이란 깨어있지만 꿈속을 헤엄치는 기분
-세상과 나의 끊임없이 계속되는 불협화음은 굳게닫힌 맘의문에 자물쇠를 걸었다
-긴긴 외로움으로 녹이슨 키를 꺼내들어 (키를 꺼내들어)
-풀리지않는 괴리감으로 나를묶은 족쇄가 내목을 조여와 (내목을 조여와)
-울리지않는 전화기를 들었다놨다 밤새도록 너를 기다려 (너를 기다려)
-나는 관심이 필요해 나는 대화가 필요해 너의 손길이 필요해 작은 사랑이 필요해
-점점 꺼져가는 도화선에 불을 지펴줘 (불을 지펴줘)
-난 여기에도 저기에도 어디에도 섞이지못해 너에게도 그녀에게도 누구에게도 속하지못해
-주위를 서성거리며 너의곁에 맴돌아 (곁에 맴돌아)
-난 여기에도 저기에도 어디에도 섞이지못해 너에게도 그녀에게도 누구에게도 속하지못해
-주위를 서성거리며 너의곁에 맴돌아 (곁에 맴돌아)
-달빛은 알아줄까 외로운 이밤을 별빛은 안아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다 그리움에 파묻혀서 그대를 부른다
-달빛은 알아줄까 외로운 이밤을 별빛은 안아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다 그리움에 파묻혀서 그대를 부른다
-주위를 서성거리며 너의곁에 맴돌아 변화가 두려워 섞이지 못하고 주위를 겉돌아
-인연의 사슬을 풀어줄 사람을 찾아 노래를 부르네 바람따라 구름따라 세상을 떠돌아
-넌 어디로 갔을까 날 버리고 머머머머 멀어진 너와 저저저저 저멀리 아무도 모르는곳으로
-떠나가고파 사랑에 굶주린 나는 언제나 배고파
-손가락질조차 그리워 관심조차 과분해서 사랑조차 사치스러워
-언제부턴가 내곁에 붙어다니는 그림자가 달을 가릴때 내맘은 너를 그린다
-난 끊임없이 주문을 외운다 내게는 너없는 하루하루가 너무나 두려워
-보고 싶어 만지고 싶어 느끼고 싶어서 말없이 마냥 습관처럼 손톱을 깨물어
-난 여기에도 저기에도 어디에도 섞이지못해 너에게도 그녀에게도 누구에게도 속하지못해
-주위를 서성거리며 너의곁에 맴돌아 (곁에 맴돌아)
-난 여기에도 저기에도 어디에도 섞이지못해 너에게도 그녀에게도 누구에게도 속하지못해
-주위를 서성거리며 너의곁에 맴돌아 (곁에 맴돌아)
-달빛은 알아줄까 외로운 이밤을 별빛은 안아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다 그리움에 파묻혀서 그대를 부른다
-달빛은 알아줄까 외로운 이밤을 별빛은 안아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다 그리움에 파묻혀서 그대를 부른다
-난 여기에도 저기에도 어디에도 섞이지못해 너에게도 그녀에게도 누구에게도 속하지못해
-주위를 서성거리며 너의곁에 맴돌아 (곁에 맴돌아)
-난 여기에도 저기에도 어디에도 섞이지못해 너에게도 그녀에게도 누구에게도 속하지못해
-주위를 서성거리며 너의곁에 맴돌아 (곁에 맴돌아)
-달빛은 알아줄까 외로운 이밤을 별빛은 안아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다 그리움에 파묻혀서 그대를 부른다
-달빛은 알아줄까 외로운 이밤을 별빛은 안아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다 그리움에 파묻혀서 그대를 부른다</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>@키에에엑</t>
-  </si>
-  <si>
-    <t>2:19 웅장한 멜로디 맛이 개지림</t>
+    <t>@wnnabe4875</t>
+  </si>
+  <si>
+    <t>2026에도 들으시는 분~~~
+안들었으면 몰라도 들은 이상 찾게되는 크랙샷</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>@wanderer6488</t>
+  </si>
+  <si>
+    <t>타협없이 세월을 견뎌온 네 명의 사내… 어떻게 이 실력으로 무명 세월을 참을 수가 있는지 궁금하다</t>
+  </si>
+  <si>
+    <t>1.1천</t>
+  </si>
+  <si>
+    <t>@리미-q8b</t>
+  </si>
+  <si>
+    <t>도대체 예지팀 2등시킨 팀이 누군지 어이가없어서 찾다가 빈세트 늪에 빠져 메들리까지 와부렀다 ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>@eyoukang7443</t>
+  </si>
+  <si>
+    <t>어떤 ㅅㅋ가 빈센트 기죽였냐 이렇게 잘하는 사람을</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>@아픈고양이신호</t>
+  </si>
+  <si>
+    <t>오디션에서 난 괜찮아는 광탈하는 필수 코스인데 이노래로 역대급을 찍어버리는 당신들은 대체….</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>@장유경-f3u</t>
+  </si>
+  <si>
+    <t>오십 중반 아줌마입니다. 
+그동안 잊고 있던 내 안에 열정을 꺼내 준 크랙샷! 그대들이여 영원하라!</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>@소율-f7g</t>
+  </si>
+  <si>
+    <t>9개월 아들내미 자장가로 효과 최고네요 메탈의 피가 흐르는 우리 아들내미</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>@꿈아재</t>
+  </si>
+  <si>
+    <t>헤비메탈을 동경하던 고등학생으로 나를 돌려 놓네요. 
+공연하면 보러 갑니다. 
+오늘도 달려주세여</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>@skehalsrksdls</t>
+  </si>
+  <si>
+    <t>슈퍼밴드 안나왔으면 어쩔뻔했냐.. 진짜 개멋있다</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>@김칸트-e5j</t>
+  </si>
+  <si>
+    <t>메탈의 불모지에서 여기까지 오는동안 얼마나 고군분투했을지가 느껴져서 약간 감정이입하게 되는 듯. 나도 내 삶에서 분투하다보면 저렇게 빛날 수 있을까 싶고. 계속 응원하게 된다. 크랙샷이 오랫동안 무대에 서는 걸 보고 싶다</t>
+  </si>
+  <si>
+    <t>1천</t>
+  </si>
+  <si>
+    <t>@sudragon41c38</t>
+  </si>
+  <si>
+    <t>윌리K가 점점 잘생겨 보인다......</t>
+  </si>
+  <si>
+    <t>923</t>
+  </si>
+  <si>
+    <t>@vegabondjune</t>
+  </si>
+  <si>
+    <t>내가 상상하던 팀이 하나 정도는 나오지 않을까 했을 때 나타난 그들... 정통 메탈 락이 피를 끓게 만든다....</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>@sugarbloodcafe</t>
+  </si>
+  <si>
+    <t>그렇구나. 누군가는 이렇게 치열하게 끝까지 하고 있었구나.</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>@sincere1189</t>
+  </si>
+  <si>
+    <t>슈퍼벤드가 좋은 이유가 다른 사람들 반응 보여주느라고 다시 돌려서 보여주는 게 없어서 좋은것같다..</t>
+  </si>
+  <si>
+    <t>@정학남</t>
+  </si>
+  <si>
+    <t>몇 만명 관중앞에서 공연을 해도 충분히 흥행 할 것 같은 느낌...</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>@LookMJ</t>
+  </si>
+  <si>
+    <t>와…달의 몰락은 진짜 페스티벌같은데서 보면 신나서 미쳐버릴것 같네요 ㅠㅠㅠㅠ 직접 보고싶다 정말</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>@DEN-pl8hq</t>
+  </si>
+  <si>
+    <t>처음 접했을 때는 '얘네 뭐지' 였는데
+난괜찮아  듣는데 '오?' 하다가
+"no no! ~ 샤라랄랄랄ㄹ롸아" 이후로ㅋㅋㅋ 푹 빠져듬</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>@방게현</t>
+  </si>
+  <si>
+    <t>그냥 눈물이 납니다. 80년대말 90년대초 메탈음악을 했던 저로써도 그저 감사하고 또 감사할 따름입니다.</t>
+  </si>
+  <si>
+    <t>@구아바-g7l</t>
+  </si>
+  <si>
+    <t>하.... 빈센트씨 목관리 잘하쇼 나 당신들 앞으로 평생 볼꺼니께</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>@지금이최고의순간</t>
+  </si>
+  <si>
+    <t>아침 잠 덜 깼을 때, 오후에 지쳐서 피곤할 때, 운동할 때 파워 업 하고 싶을 때, 초저녁 밥 먹고 졸릴 때, 스트레스 받을 때, 자기 전에 머리 속에 생각날 때마다 들어요. 만병통치약이자 중독약물 !!!</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>@주기적인</t>
+  </si>
+  <si>
+    <t>'경연' 하러 와서 '공연'하는 밴드</t>
+  </si>
+  <si>
+    <t>@VidroSapatos</t>
+  </si>
+  <si>
+    <t>첫인상은 겉보기에 뭔가 오바스럽다였다면 그게 매력이라 매번 무대가 기대가 되고 지금은 최애팀이 되었음</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>@jeremy3some</t>
+  </si>
+  <si>
+    <t>애네들 첨봤을땐 겉멋든 양아치인줄 알았는데..
+난 괜찮아에서 뿅가리...
+윌리K 치는거 보믄 얼굴과 매치 않되게 진짜 개간지...
+나머지 멤버도 말할것 없음.. 굳!!</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>@수범아빠</t>
+  </si>
+  <si>
+    <t>나..노래들으러..
+오늘..또..왔다~~~~
+내일 또 올게~~~</t>
+  </si>
+  <si>
+    <t>@wayneyoon</t>
+  </si>
+  <si>
+    <t>진짜 누구하나 빠짐없이 너무 잘하네 ㅎㄷㄷ 특히 갠적으론 빈센트같은 보컬을 우리나라에서 볼수있을줄은 생각도 못함</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>@kimjoobalradio</t>
+  </si>
+  <si>
+    <t>국내에서도 락이 다시 부흥하기를 바라며…</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>@sunghwoa</t>
+  </si>
+  <si>
+    <t>슈퍼밴드가 정말 좋은 이유는 밴드음악은 에너지가 넘쳐나기 때문에 참가자들이 경연임에도 불구하고 다들 각자의 음악을 존중해주고 그 에너지에 취해 진심 날뛰는 리액션을 있다는걸 볼 수 있어서 정말 좋다.</t>
+  </si>
+  <si>
+    <t>580</t>
+  </si>
+  <si>
+    <t>@임명숙-c3l</t>
+  </si>
+  <si>
+    <t>여기까지
+잘참고
+인내하신
+결과입니다
+대단하신
+분들
+최고</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>@살의추억</t>
+  </si>
+  <si>
+    <t>이분들 무대에서 내려오면 그리 착할수가 없는데 무대위의 카리스마는 ㄷㄷ</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>@jonesonpapa7516</t>
+  </si>
+  <si>
+    <t>현재 이 시대를 살아가고 최선을 다하는 bts 같은 아이돌들의 노력이나 실력을 무시하는 의미는 아닙니다만,
+음악이라는 것이 여러장르가 같이 공존했으면 합니다.
+과거 90년대 처럼 말예요.</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>@tjrgus1107</t>
+  </si>
+  <si>
+    <t>아무리봐도 장난감총은 진짜 아이디어 개쩐다 ㅋㅋㅋㅋ</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>@그응이</t>
+  </si>
+  <si>
+    <t>크랙샷 진짜 이 프로그램을 통해서 알게 됐는데
+진짜 이제라도 알게되서 너무 다행인것같다ㅠㅠㅠㅠㅠㅠ
+제발 제발 더 더더더더 많은 사람들이 알았으면 좋겠다</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>@helenk7619</t>
+  </si>
+  <si>
+    <t>이 팀만 모아주셔서 감사드려요. 찾아다니기 번거러웠거든요. ㅋㅋ 평생 처음 접한 강렬한 사운드 인데 피가 끓고, 몸이 저절로 움직이고, 소리지르고...  어머, 내게도 이런 면이 있었나? 집에 혼자 있을 때엔 스스로 미쳐서 피식 웃으며... ㅋㅋ
+나름 평생 우아와 고상을 목표로 추구했... 이제 60인데...  우짜지요?</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>@needmore_fish</t>
+  </si>
+  <si>
+    <t>와..진짜 사이다 마신것처럼 시원하네..
+코로나 끝나면 공연 꼭간다..</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>@지선한-z4b</t>
+  </si>
+  <si>
+    <t>마흔 넘어서 알았어 나 락 좋아한다는 것을.공연만 하이소 돈줄내주러 갈게용</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>@wwgd1017</t>
-  </si>
-  <si>
-    <t>가사 진짜 대박 잘썻다....속사포랩하는 음유시인ㄷㄷ</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>@수산나-y6n</t>
-  </si>
-  <si>
-    <t>인간관계에 지쳐서 힘들때 들으면 한없이 눈물나는 노래... ㅠㅠ</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>@뭐다안된대</t>
-  </si>
-  <si>
-    <t>2026에도 들으러 온 사람들 손</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>@cksaldlfp123</t>
-  </si>
-  <si>
-    <t>고등학교때 힘들었을 때 쉬는 시간에 엎드려서 이 노래 들으면서 위로받고 버텼는데 지금 들어도 가사가 너무 좋다</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>@김준희-w4g</t>
-  </si>
-  <si>
-    <t>2025년인데 이거 보는 사람 출석체크 하자</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>@gwg0112</t>
-  </si>
-  <si>
-    <t>외롭고 힘들고 자살 생각만 했던 우울했던 시절에 이 노래 들으면서 버텼던 기억이 나네...</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>@광부캐논진심</t>
-  </si>
-  <si>
-    <t>진짜 가사도 너무 좋고 리듬도 좋고 슬프고 간절한 감정이 제대로 실려가지고 너무 좋다...</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>@ParkSimBa</t>
-  </si>
-  <si>
-    <t>왜 하자고 해 왜 하자고 해</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>@자유-f8u</t>
-  </si>
-  <si>
-    <t>아웃사이더 노래들을 때마다 생각하는거:이건 아웃사이더 밖에 못 부른다</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>@자몽-q8s</t>
-  </si>
-  <si>
-    <t>아 진짜 몇 백번을 들었는데, 갑자기 외톨이 알고리즘 떠서 여기까지 왔네ㅠㅜ</t>
-  </si>
-  <si>
-    <t>@Scarycatnextdoor</t>
-  </si>
-  <si>
-    <t>와 이거 내 초딩때 최애곡인데ㅋㅋㅋㅋㅋㅠㅜㅠㅠ이거 켜놓고 그랜드체이스 뚝딱 조졌었는데 그립다</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>@Icestar-v3l</t>
-  </si>
-  <si>
-    <t>핵공감 가사가 나의 심금을 울리네..</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>@김동민-r3</t>
-  </si>
-  <si>
-    <t>삶에 대한 열정이나 희망 따위는 없어
-흘러가는대로 그냥 숨쉬고 있을뿐
-무미건조하게 매일 반복 되는 일상이란
-깨어 있지만 꿈 속을 헤엄치는 기분
-세상과 나의 끊임없이 계속되는 불협화음
-굳게 닫힌 마음의 문에 자물쇠를 걸었다
-(긴 긴) 외로움으로 녹이슨 키를 꺼내들어 (키를 꺼내들어)
-풀리지 않는 괴리감으로 나를 묶은 족쇄가
-내 목을 조여와 (내 목을 조여와)
-울리지않는 전화기를 들었다 놨다
-밤새도록 너를 기다려 (너를 기다려)
-나는 관심이 필요해 나는 대화가 필요해
-너의 손길이 필요해 작은 사랑이 필요해
-점점 꺼져가는 도화선에 불을 지펴줘 (불을 지펴줘)
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아 (곁을 맴돌아)
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아 (곁을 맴돌아)
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-주위를 서성거리며 너의 곁을 맴돌아
-변화가 두려워 섞이지 못하고 주위를 겉돌아
-인연의 사슬을 풀어 줄 사람을 찾아 노래를 부르네
-바람따라 구름따라 세상을 떠돌아
-넌 어디로 갔을까 날 버리고 머머머머머 멀어진
-너마저 저저저저저 저 멀리 아무도 모르는곳으로
-떠나가고파 사랑에 굶주린 나는 언제나 배고파
-손가락질 조차 그리워
-관심조차 과분해서 사랑조차 사치스러워
-언제부턴가 내 곁에 붙어 다니는 그림자가
-달을 가릴때 내 마음은 너를 그린다
-난 끊임없이 주문을 외운다
-내게는 너 없는 하루하루가 너무나 두려워
-보고 싶어 만지고 싶어 느끼고 싶어도
-말없이 마냥 습관처럼 손톱을 깨물어
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아 (곁을 맴돌아)
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아 (곁을 맴돌아)
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다</t>
+    <t>@선한영향력-o6o</t>
+  </si>
+  <si>
+    <t>제발 이 장르 그대로 변치말고 우리곁에 남아주세요.
+멋있다 못해 존경스럽기까지 합니다.
+대기만성 고진감래가 이런거죠.
+정말 콘서트장이었다면 저 목 다 쉬었을겁니다. 
+슈밴 우승하고 전국 콘서트 해외 콘서트까지 이젠 꽃길만 걸으세요.
+그동안 정말 고생많으셨습니다.
+계속 응원할께요.</t>
   </si>
   <si>
     <t>52</t>
   </si>
   <si>
-    <t>@gpa223</t>
-  </si>
-  <si>
-    <t>직장은 돈벌려고 가는건데 왜 인간관계때문에 이리 힘든지 ㅠㅠ</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>@MrAls6538</t>
-  </si>
-  <si>
-    <t>이 시절에 mp3에 다운 받아서 아웃사이더 전곡 산책하면서 들었는데 그 때 그 감성이 잊히지 않는다. 그 때로 돌아가고 싶다</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>@buddy3832</t>
-  </si>
-  <si>
-    <t>아웃사이더 최고의 명곡</t>
-  </si>
-  <si>
-    <t>@Eren-6666</t>
-  </si>
-  <si>
-    <t>2019년에 들어도 좋네 노래가... 한때 차트 휩쓸었던덴 다 이유가 있다</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>@psu01016</t>
-  </si>
-  <si>
-    <t>외톨이도 좋지만 이 곡이 최고다...</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>@TV-or2zd</t>
-  </si>
-  <si>
-    <t>반주 음 존나좋네</t>
-  </si>
-  <si>
-    <t>@흉부외과전문오랑</t>
-  </si>
-  <si>
-    <t>어렸을 때 그렇게 좋아했었는데 왜 그렇게 좋아했나 싶을 때마다 한 번씩 들으면 아 좋아할만했다 싶은 래퍼 랩 잘하는 사람이야 그때나 지금이나 많았지만 아웃사이더 특유의 감성은 아직도 독보적이라고 느껴지네</t>
-  </si>
-  <si>
-    <t>@loadbang1</t>
-  </si>
-  <si>
-    <t>전 어디에 속해야 하는걸까요...여기를가도 저기를 가도 섞이지 못하고 겉도네요.잘하고 싶은데 안되는 심정을 다들 무시하니 저도 아웃사이더 마인드가 생기더군요.그냥...뭐랄까...굳이 섞이려는 시도를 하는 에너지가 아까워서 그냥 지켜봐요.어차피 인생은 혼자. 그럴 팔자라면...겉도는대로 살아갈려구요.</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>@TV-qt2zr</t>
-  </si>
-  <si>
-    <t>아웃사이더는 랩을 너무잘함ㅇㅈ.</t>
+    <t>@이계수-o1p</t>
+  </si>
+  <si>
+    <t>천재를  넘어선 괴물이다 우리 음악사를 새로 쓸것이다.  세계 탑이 되어라</t>
+  </si>
+  <si>
+    <t>@81산티아고</t>
+  </si>
+  <si>
+    <t>고2때부터 메탈 좋아한 50대 초반 아줌마입니다.
+우리나라에서는 락 메탈이 자리잡지 못해
+안타까운데 이 시점으로  한자리 굳건히 지켜
+나가길 바랍니다.</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>@심플is최고</t>
+  </si>
+  <si>
+    <t>빈센트 목관리 잘 해서 오래보자!!!
+크랙샷 흥해라~!!!</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>@안라빈</t>
+  </si>
+  <si>
+    <t>빈센트님 제발 오늘 살아남아주세요
+아니 윌리K, 싸이언, 대니 리 다 살아줘요 ㅠㅠ
+다른팀으로 찢어져도 다 살아남아줘 제발</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>@지희나-m4f</t>
+  </si>
+  <si>
+    <t>와ㅡㅡ너무잘해 이것이 k락이다 가자 세계로 크렉샷 빈센트 윌리k 격하게 사랑한다</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>@zzung7704</t>
+  </si>
+  <si>
+    <t>5:59 아 진짜 이 대목엔 쵸프라까야맹키로
+리액션이 안나올 수 없다.
+뭐지? 아 그냥 아련하고 아프고 저림!
+진짜 직접 보고 싶다아아아아아아아아</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>@irene_982</t>
+  </si>
+  <si>
+    <t>난 괜찮아 에서 빈센트가 No no 할때가 너무 좋아서 몇번을 돌려봐요..그 목소리랑 눈이 왤케 멋져보이죠ㅜㅜ</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>@HSK9134</t>
+  </si>
+  <si>
+    <t>싱어게인 정홍일에 이어 슈퍼밴드에서는 크랙샷 까지 나와주셔서 너무 감사합니다 이런 아티스트들 보려고 오디션 프로 챙겨봅니다. 대한민국 록은 죽지 않습니다!!!</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>@노량진이영화</t>
+  </si>
+  <si>
+    <t>에이~아무리 그래도 그렇지
+어떻게 윌리k가 
+잘 생겨보일수가 있,,,,네???
+여보세요??? 여보세요???</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>@김성운-r1c</t>
+  </si>
+  <si>
+    <t>그동안 얼마나 힘들었고 노력했을까?
+앞으로 꽃길만 걷자 크랙샷!!!!!</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>@심호윤-h3t</t>
+  </si>
+  <si>
+    <t>능력만있다면 단독 콘서트해주고싶다.
+기타리스트는 무대매너가B'Z라는 그룹을 생각나게하네.
+물론 더 훨씬 월등하지만..
+오십중반인 나도 반했다.
+그저 오디션이아닌 자신들을 더 알리기위해 나온듯..
+심사위원 누구도 이들을 평가하기엔 너무 멋있고 음악도 너무 잘해.많은 골수팬이 생길듯..</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>@joykim400</t>
+  </si>
+  <si>
+    <t>난 분명 메탈을 싫어하는 사람인데. . . 왜왜 크랙샷은 왜 경연 때마다 좋은걸까요?! 당신들 대체 뭐야!</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>@ricechickencutlet</t>
+  </si>
+  <si>
+    <t>진짜 난 괜찮아는 다른 영상들에 비해서 편집도 너무 잘 된 거 같다...
+편집하신 분 음잘알에 밴잘알이신 듯</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>@inchoi9171</t>
+  </si>
+  <si>
+    <t>월급 55만원 받으면서 아둥바둥 버텨내던 스무살 그 때...눈물도 많고 서러움도 많고 아버지는 왜 그렇게 일찍 세상을 떠나셨나....대학 다니는 친구들이 부러워 눈물이 찔끔 났던 그때의 나의 힘, 나의 락, 나의 노래...스무살의 나... 아직 살아있었구나...</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>@leego22</t>
+  </si>
+  <si>
+    <t>이런 음악은 락페에서 들어야 되는데</t>
+  </si>
+  <si>
+    <t>@yob2862</t>
+  </si>
+  <si>
+    <t>진짜 달의 몰락에서 윌리케이 소울 담긴 오카리나 ㅋㅋㅋㅋ 어쩜 그렇게 조신한지 ㅋㅋㅋㅋ</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>@부산명지미러클영어</t>
+  </si>
+  <si>
+    <t>대학축제 행사에 초청 공연하면 넘 흥분될 것 같아요. 모든 멤버가 정감가는 밴드는 처음인것 같아요. 락을 지금까지 좋아한적 한번도 없는데 크랙샷은 빠져드네요. ㅎ</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>@havefun-t7j</t>
+  </si>
+  <si>
+    <t>해비메탈  한번도 
+조아해본적 없다 그런데 ~~~~~~어느날 내안에 크랙샷이 들어왓다~~~~~</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>@시골정원-j8e</t>
+  </si>
+  <si>
+    <t>4명 모두 찐 아트맨~
+지난 무명을 발판으로
+한국 음악사에 진심으로 영원하길~~~!!!!!!!!!!</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>@kosanja5073</t>
+  </si>
+  <si>
+    <t>이렇게 멋진 밴드가 살아있는 것 자체가 기적입니다. 정말 감사합니다.</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>우리곁에서 
+함께   하기를
+응원합니다</t>
+  </si>
+  <si>
+    <t>@왓따-e7i</t>
+  </si>
+  <si>
+    <t>연달아보니 3배로 화끈하네요 ㅋㅋㅋㅋㅋㅋㅋ</t>
+  </si>
+  <si>
+    <t>@착하게살자-x7b</t>
+  </si>
+  <si>
+    <t>슈퍼밴드1 준우승팀 퍼플레인은 경연때는 롹,메탈장르로 흥분시키더니 기획사 들어가서 음악이 완전변해버린거 같은데 크랙샷은 오은철군 포함해서 5인조로 계속 자기음악을 했으면 좋겠습니다.크랙샷 화이팅 베이스도,드럼도,기타도,보컬도 오은철군도 끝내줍니다. ^^</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>@cortlee72</t>
+  </si>
+  <si>
+    <t>크랙샷 정말 대단한그룹 입니다. 불모지한국에서 이런실력을 키우는게 쉽지 않은데 정말 존경합니다.</t>
   </si>
   <si>
     <t>65</t>
-  </si>
-  <si>
-    <t>@김동욱-k6s</t>
-  </si>
-  <si>
-    <t>진짜 아웃사이더노래는 소름끼치도록 노래가 좋아...ㅎㄷㄷ 먼가가</t>
-  </si>
-  <si>
-    <t>@RedFox-RFX</t>
-  </si>
-  <si>
-    <t>사람 사귀는게 제일 어려운거라는거 확연히 깨닫음</t>
-  </si>
-  <si>
-    <t>@민수심-p7f</t>
-  </si>
-  <si>
-    <t>노래가 슬프다....
-그러면서 좋다.</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>@풍선껌a</t>
-  </si>
-  <si>
-    <t>힝힝ㅠ가사엄더</t>
-  </si>
-  <si>
-    <t>@돼지국밥전도사</t>
-  </si>
-  <si>
-    <t>진짜 존나게 좋은데 존나게 슬프고 존나게 우울하게 만드는 노래다</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>@bluegm2713</t>
-  </si>
-  <si>
-    <t>따라부르기 진짜.. 아웃사이더는 전설이다</t>
-  </si>
-  <si>
-    <t>@mk9nzm6</t>
-  </si>
-  <si>
-    <t>omg the blend of classical instruments and Outsider's rap is perfect!</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>@benatakr</t>
-  </si>
-  <si>
-    <t>아웃사이더 완전 좋음ㅎㅎㅎㅎ</t>
-  </si>
-  <si>
-    <t>@ab-qy1xm</t>
-  </si>
-  <si>
-    <t>아웃사이더 랩 특징: 다른사람과 다르게 빠르게 (랩을)하는데 다 들리고 깔끔하게 사라짐(심지어 가사까지 좋음)
-근데 너무 깔끔하게사라져서 곡 듣고나면 '어? 내가 뭘 들었었지??'라는 생각이 들음 ㅋㅋㅋㅋㅋ</t>
-  </si>
-  <si>
-    <t>@JGJ-zx6rz</t>
-  </si>
-  <si>
-    <t>외톨이 주변인 2연타는 진짜 ㅠㅠ</t>
-  </si>
-  <si>
-    <t>@권보근-f4b</t>
-  </si>
-  <si>
-    <t>난 수시에도 정시에도 어디에도 속하지 못해</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>@wjddbsgh</t>
-  </si>
-  <si>
-    <t>뮤비를 이해한다면 당신은 천재입니다!</t>
-  </si>
-  <si>
-    <t>@드라마모노</t>
-  </si>
-  <si>
-    <t>이런 류의노래가 많이 나왔으면좋겠다</t>
-  </si>
-  <si>
-    <t>@ookkkok6962</t>
-  </si>
-  <si>
-    <t>아 가사 진짜 공감...ㅠㅠㅠ</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>@약사-e2d</t>
-  </si>
-  <si>
-    <t>외톨이에서 주변인이돼고 주인공이돼는건가</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>@hsko7887</t>
-  </si>
-  <si>
-    <t>왜 요즘은 이런 노래불러주는 가수가 없울까요</t>
   </si>
 </sst>
 </file>
@@ -521,7 +658,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="@jihunyang1556"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="@wnnabe4875"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -559,7 +696,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="@키에에엑"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="@wanderer6488"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -597,7 +734,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="@wwgd1017"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="@리미-q8b"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -635,7 +772,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="@수산나-y6n"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="@eyoukang7443"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -673,7 +810,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="@뭐다안된대"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="@아픈고양이신호"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -711,7 +848,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="@cksaldlfp123"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="@장유경-f3u"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -749,7 +886,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="@김준희-w4g"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="@소율-f7g"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -787,7 +924,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="@gwg0112"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="@꿈아재"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -825,7 +962,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="@광부캐논진심"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="@skehalsrksdls"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -852,7 +989,197 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10" descr="@김칸트-e5j"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="1905000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11" descr="@sudragon41c38"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2095500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12" descr="@vegabondjune"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2286000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13" descr="@sugarbloodcafe"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2476500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14" descr="@sincere1189"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2667000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
@@ -863,13 +1190,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="@김동민-r3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <xdr:cNvPr id="16" name="Picture 15" descr="@정학남"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -901,13 +1228,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11" descr="@gpa223"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <xdr:cNvPr id="17" name="Picture 16" descr="@LookMJ"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -939,13 +1266,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12" descr="@MrAls6538"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <xdr:cNvPr id="18" name="Picture 17" descr="@DEN-pl8hq"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -977,13 +1304,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13" descr="@buddy3832"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <xdr:cNvPr id="19" name="Picture 18" descr="@방게현"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1015,13 +1342,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14" descr="@Eren-6666"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <xdr:cNvPr id="20" name="Picture 19" descr="@구아바-g7l"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1053,13 +1380,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15" descr="@psu01016"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <xdr:cNvPr id="21" name="Picture 20" descr="@지금이최고의순간"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1091,13 +1418,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16" descr="@TV-or2zd"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <xdr:cNvPr id="22" name="Picture 21" descr="@주기적인"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1129,13 +1456,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17" descr="@흉부외과전문오랑"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <xdr:cNvPr id="23" name="Picture 22" descr="@VidroSapatos"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1167,13 +1494,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 18" descr="@loadbang1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <xdr:cNvPr id="24" name="Picture 23" descr="@jeremy3some"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1205,13 +1532,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 19" descr="@TV-qt2zr"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <xdr:cNvPr id="25" name="Picture 24" descr="@수범아빠"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1243,13 +1570,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 20" descr="@김동욱-k6s"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <xdr:cNvPr id="26" name="Picture 25" descr="@wayneyoon"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1281,13 +1608,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 21" descr="@RedFox-RFX"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <xdr:cNvPr id="27" name="Picture 26" descr="@kimjoobalradio"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1319,13 +1646,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Picture 22" descr="@민수심-p7f"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <xdr:cNvPr id="28" name="Picture 27" descr="@sunghwoa"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1333,6 +1660,500 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1828800" y="5143500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Picture 28" descr="@irene_982"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="8191500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 29" descr="@HSK9134"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="8382000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Picture 30" descr="@노량진이영화"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="8572500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Picture 31" descr="@김성운-r1c"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="8763000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Picture 32" descr="@심호윤-h3t"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="8953500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Picture 33" descr="@joykim400"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="9144000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Picture 34" descr="@ricechickencutlet"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="9334500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 35" descr="@inchoi9171"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="9525000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 36" descr="@leego22"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="9715500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Picture 37" descr="@yob2862"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="9906000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 38" descr="@부산명지미러클영어"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="10096500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 39" descr="@havefun-t7j"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="10287000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Picture 40" descr="@시골정원-j8e"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="10477500"/>
           <a:ext cx="419100" cy="419100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1630,7 +2451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1756,36 +2577,27 @@
       <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1798,9 +2610,6 @@
       <c r="C14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
@@ -1810,98 +2619,95 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
         <v>46</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
         <v>49</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>50</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
         <v>57</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
         <v>60</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
-        <v>64</v>
-      </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
         <v>65</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>66</v>
-      </c>
-      <c r="C23" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1923,18 +2729,18 @@
         <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" t="s">
         <v>73</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1945,197 +2751,441 @@
         <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" t="s">
         <v>84</v>
-      </c>
-      <c r="D30" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" t="s">
         <v>84</v>
-      </c>
-      <c r="D38" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>135</v>
+      </c>
+      <c r="B47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>141</v>
+      </c>
+      <c r="B49" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>144</v>
+      </c>
+      <c r="B50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" t="s">
+        <v>148</v>
+      </c>
+      <c r="C51" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>150</v>
+      </c>
+      <c r="B52" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" t="s">
+        <v>153</v>
+      </c>
+      <c r="C53" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" t="s">
+        <v>156</v>
+      </c>
+      <c r="C54" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>161</v>
+      </c>
+      <c r="B56" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" t="s">
+        <v>166</v>
+      </c>
+      <c r="D57" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" t="s">
+        <v>167</v>
+      </c>
+      <c r="C58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>168</v>
+      </c>
+      <c r="B59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C59" t="s">
+        <v>154</v>
+      </c>
+      <c r="D59" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>170</v>
+      </c>
+      <c r="B60" t="s">
+        <v>171</v>
+      </c>
+      <c r="C60" t="s">
+        <v>172</v>
+      </c>
+      <c r="D60" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>173</v>
+      </c>
+      <c r="B61" t="s">
+        <v>174</v>
+      </c>
+      <c r="C61" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
